--- a/artfynd/A 22965-2026 artfynd.xlsx
+++ b/artfynd/A 22965-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,57 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>134623869</v>
+        <v>134637826</v>
       </c>
       <c r="B2" t="n">
-        <v>99195</v>
+        <v>80492</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>6461</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(L.) Torss.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Mört-tjärnen, Mört-tjärnen, Jmt</t>
+          <t>Yxskafttjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>487389</v>
+        <v>487355</v>
       </c>
       <c r="R2" t="n">
-        <v>6979494</v>
+        <v>6979504</v>
       </c>
       <c r="S2" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -754,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>17:36</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -764,12 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>17:36</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>+2 vinterståndare</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -789,10 +775,462 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
+          <t>Ludvig Nordin</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>134637824</v>
+      </c>
+      <c r="B3" t="n">
+        <v>57162</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Yxskafttjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>487359</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6979505</v>
+      </c>
+      <c r="S3" t="n">
+        <v>8</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Näs</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>14:10</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>14:10</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>1 ex</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Ludvig Nordin</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Ludvig Nordin</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>134637825</v>
+      </c>
+      <c r="B4" t="n">
+        <v>58131</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>103023</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Tofsmes</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Lophophanes cristatus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Yxskafttjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>487356</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6979504</v>
+      </c>
+      <c r="S4" t="n">
+        <v>3</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Näs</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>14:11</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>14:11</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>1 ex lockläte</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Ludvig Nordin</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Ludvig Nordin</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>134623869</v>
+      </c>
+      <c r="B5" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Mört-tjärnen, Mört-tjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>487389</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6979494</v>
+      </c>
+      <c r="S5" t="n">
+        <v>7</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Näs</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>17:36</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>17:36</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>+2 vinterståndare</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Ludvig Nordin</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
           <t>Ludvig Nordin, Fredrik Jonsson, Ulrika Nordin</t>
         </is>
       </c>
-      <c r="AY2" t="inlineStr"/>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>134637852</v>
+      </c>
+      <c r="B6" t="n">
+        <v>80492</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>6461</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Norrlandslav</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Nephroma arcticum</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(L.) Torss.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Yxskafttjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>487630</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6979578</v>
+      </c>
+      <c r="S6" t="n">
+        <v>9</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Näs</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>18:05</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>18:05</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Ludvig Nordin</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Ludvig Nordin</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 22965-2026 artfynd.xlsx
+++ b/artfynd/A 22965-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134637826</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -891,6 +901,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134637824</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1003,6 +1018,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134637825</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1124,6 +1144,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134623869</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1231,8 +1256,20 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134637852</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>